--- a/downloads/indicadores/IGAE/IGAE_datos.xlsx
+++ b/downloads/indicadores/IGAE/IGAE_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -577,14 +577,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>May 25 R</t>
+          <t>Ene 18</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45778</v>
+        <v>43101</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>107.407876</v>
+        <v>97.40575</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -635,18 +635,18 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Jun 25 R</t>
+          <t>Feb 18</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45809</v>
+        <v>43132</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>104.50353</v>
+        <v>95.318709</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -693,18 +693,18 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Jul 25 R</t>
+          <t>Mar 18</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45839</v>
+        <v>43160</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>105.661466</v>
+        <v>98.983662</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -751,18 +751,18 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Ago 25 R</t>
+          <t>Abr 18</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>45870</v>
+        <v>43191</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>104.822875</v>
+        <v>98.914811</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -809,18 +809,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Sep 25 R</t>
+          <t>May 18</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45901</v>
+        <v>43221</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>103.226895</v>
+        <v>102.012664</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -867,18 +867,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Oct 25 R</t>
+          <t>Jun 18</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>45931</v>
+        <v>43252</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>107.920791</v>
+        <v>101.245537</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -925,18 +925,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nov 25 R</t>
+          <t>Jul 18</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45962</v>
+        <v>43282</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>107.829456</v>
+        <v>100.145819</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -983,18 +983,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Dic 25 R</t>
+          <t>Ago 18</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45992</v>
+        <v>43313</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>107.41679</v>
+        <v>101.605918</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -1041,18 +1041,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Ene 26 R</t>
+          <t>Sep 18</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>46023</v>
+        <v>43344</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>100.928378</v>
+        <v>97.99775699999999</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1099,18 +1099,18 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Feb 26 R</t>
+          <t>Oct 18</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>46054</v>
+        <v>43374</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>100.121986</v>
+        <v>102.342492</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -1157,18 +1157,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Mar 26 P</t>
+          <t>Nov 18</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>46082</v>
+        <v>43405</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>106.956932</v>
+        <v>104.005919</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1215,18 +1215,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Abr 26 P</t>
+          <t>Dic 18</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>46113</v>
+        <v>43435</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>106.675953</v>
+        <v>100.020963</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1273,56 +1273,5160 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Ene 19</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>98.524359</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Feb 19</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>43497</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>95.935875</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Mar 19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>43525</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>99.92981399999999</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Abr 19</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>97.675476</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>May 19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>43586</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>101.335635</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Jun 19</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>43617</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>99.86584499999999</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Jul 19</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>43647</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>100.509023</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Ago 19</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>43678</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>100.135087</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sep 19</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>43709</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>97.49269700000001</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Oct 19</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>43739</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>100.541717</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Nov 19</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>43770</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>102.895474</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Dic 19</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>43800</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>99.932557</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ene 20</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>98.307236</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Feb 20</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>43862</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>95.26016199999999</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mar 20</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>43891</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>96.923638</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Abr 20</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>76.33145500000001</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43952</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>76.902247</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Jun 20</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>43983</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>86.481436</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>90.45550299999999</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Ago 20</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>44044</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>91.53083700000001</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sep 20</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>44075</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>92.965862</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Oct 20</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>96.35490799999999</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nov 20</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>44136</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>99.300853</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Dic 20</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>44166</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>97.984786</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Ene 21</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>93.118089</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Feb 21</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>44228</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>90.873041</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Mar 21</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>44256</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>99.807293</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Abr 21</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>96.193974</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>44317</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>98.212221</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>44348</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>98.427244</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Jul 21</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>97.30561299999999</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Ago 21</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>44409</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>96.06193399999999</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sep 21</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>44440</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>93.724242</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Oct 21</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>96.266563</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Nov 21</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>44501</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>101.089458</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Dic 21</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>44531</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>99.655911</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Ene 22</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>94.772383</v>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Feb 22</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>44593</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>93.60069</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>44621</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>101.591719</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Abr 22</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>98.48142199999999</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>44682</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>101.619992</v>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>44713</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>100.245379</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Jul 22</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>99.70265000000001</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Ago 22</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>44774</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>101.692771</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Sep 22</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>44805</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>98.85154900000001</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Oct 22</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>100.790922</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Nov 22</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>44866</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>105.840784</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Dic 22</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>44896</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>103.995015</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Ene 23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>99.333044</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Feb 23</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>44958</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>97.086805</v>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>44986</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>104.12209</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Abr 23</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>100.253502</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>45047</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>105.869797</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>45078</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>104.089404</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Jul 23</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>102.785593</v>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Ago 23</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>45139</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>105.066281</v>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Sep 23</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>45170</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>102.623346</v>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Oct 23</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>105.333122</v>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Nov 23</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>45231</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>107.716653</v>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Dic 23</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>104.537535</v>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Ene 24</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>101.705954</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Feb 24</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>45323</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>101.369399</v>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Mar 24</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>102.722816</v>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Abr 24</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>105.729093</v>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>May 24</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>45413</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>107.473172</v>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>45444</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>103.563014</v>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Jul 24</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>106.832965</v>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Ago 24</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>45505</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>105.571206</v>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Sep 24</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>45536</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>102.548587</v>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Oct 24</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>106.14003</v>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Nov 24</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>45597</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>108.058006</v>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Dic 24</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>45627</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>103.984594</v>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Ene 25</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>101.348475</v>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Feb 25</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>45689</v>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>100.491729</v>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>45717</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>105.467563</v>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Abr 25</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>104.009094</v>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>May 25 R</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>107.407876</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Jun 25 R</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>104.50353</v>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>+0.2%</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>+0.9%</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Jul 25 R</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>105.661466</v>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>-1.2%</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Ago 25 R</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>104.822875</v>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Sep 25 R</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>103.226895</v>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Oct 25 R</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>107.920791</v>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>+1.6%</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Nov 25 R</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>107.829456</v>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>+1.1%</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Dic 25 R</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>107.41679</v>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>+2.4%</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Ene 26 R</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>100.928378</v>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26 R</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>100.121986</v>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Mar 26 P</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>106.956932</v>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Abr 26 P</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>106.675953</v>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>23 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B106" s="5" t="n">
         <v>46143</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C106" s="6" t="n">
         <v>108.595752</v>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D106" s="4" t="inlineStr">
         <is>
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>+2.0%</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Índice base 2018=100</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
         <is>
           <t>23 de julio de 2026</t>
         </is>

--- a/downloads/indicadores/IGAE/IGAE_datos.xlsx
+++ b/downloads/indicadores/IGAE/IGAE_datos.xlsx
@@ -5344,7 +5344,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">

--- a/downloads/indicadores/IGAE/IGAE_datos.xlsx
+++ b/downloads/indicadores/IGAE/IGAE_datos.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121 · Fecha de publicación: 23 de julio de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf · Fecha de publicación: 23 de julio de 2026</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">

--- a/downloads/indicadores/IGAE/IGAE_datos.xlsx
+++ b/downloads/indicadores/IGAE/IGAE_datos.xlsx
@@ -5681,7 +5681,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>May 25 R</t>
+          <t>May 25</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -5739,7 +5739,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Jun 25 R</t>
+          <t>Jun 25</t>
         </is>
       </c>
       <c r="B95" s="8" t="n">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Jul 25 R</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -5855,7 +5855,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Ago 25 R</t>
+          <t>Ago 25</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Sep 25 R</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -5971,7 +5971,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Oct 25 R</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B99" s="8" t="n">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
@@ -6029,7 +6029,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Nov 25 R</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -6087,7 +6087,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Dic 25 R</t>
+          <t>Dic 25</t>
         </is>
       </c>
       <c r="B101" s="8" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -6145,7 +6145,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Ene 26 R</t>
+          <t>Ene 26</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
@@ -6203,7 +6203,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Feb 26 R</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B103" s="8" t="n">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -6261,7 +6261,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Mar 26 P</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -6319,7 +6319,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Abr 26 P</t>
+          <t>Abr 26</t>
         </is>
       </c>
       <c r="B105" s="8" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">

--- a/downloads/indicadores/IGAE/IGAE_datos.xlsx
+++ b/downloads/indicadores/IGAE/IGAE_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O406"/>
+  <dimension ref="A1:O407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf · Fecha de publicación: 23 de julio de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf · Fecha de publicación: 24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O14" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O16" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O28" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O32" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O36" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O38" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2415,12 +2415,12 @@
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O40" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O42" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2580,12 @@
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O44" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2690,12 @@
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O46" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2855,12 +2855,12 @@
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O48" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O50" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3075,12 +3075,12 @@
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O52" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3185,12 @@
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O54" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O56" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O58" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3625,12 @@
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3735,12 +3735,12 @@
       </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O64" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O65" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3845,12 @@
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O66" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O67" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3955,12 +3955,12 @@
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O68" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O69" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4065,12 +4065,12 @@
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O70" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4120,12 @@
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4175,12 @@
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O72" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4285,12 @@
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O74" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4340,12 @@
       </c>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O76" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O78" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O80" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4670,12 @@
       </c>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O81" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O82" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4780,12 +4780,12 @@
       </c>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O83" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4835,12 +4835,12 @@
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O84" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O85" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O86" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5000,12 +5000,12 @@
       </c>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O87" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="N88" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O88" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5110,12 +5110,12 @@
       </c>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O89" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O90" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5220,12 +5220,12 @@
       </c>
       <c r="N91" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O91" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="N92" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O92" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="N93" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O93" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="N94" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O94" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O95" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="N96" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O96" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5550,12 @@
       </c>
       <c r="N97" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O97" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="N98" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O98" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5660,12 +5660,12 @@
       </c>
       <c r="N99" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O99" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5715,12 +5715,12 @@
       </c>
       <c r="N100" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O100" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="N101" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O101" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="N102" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O102" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5880,12 +5880,12 @@
       </c>
       <c r="N103" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O103" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5935,12 +5935,12 @@
       </c>
       <c r="N104" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O104" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5990,12 +5990,12 @@
       </c>
       <c r="N105" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O105" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="N106" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O106" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="N107" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O107" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6155,12 +6155,12 @@
       </c>
       <c r="N108" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O108" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="N109" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O109" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6265,12 @@
       </c>
       <c r="N110" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O110" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6320,12 +6320,12 @@
       </c>
       <c r="N111" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O111" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="N112" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O112" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6430,12 +6430,12 @@
       </c>
       <c r="N113" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O113" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6485,12 +6485,12 @@
       </c>
       <c r="N114" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O114" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6540,12 +6540,12 @@
       </c>
       <c r="N115" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O115" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="N116" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O116" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="N117" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O117" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="N118" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O118" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="N119" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O119" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="N120" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O120" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="N121" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O121" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="N122" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O122" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="N123" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O123" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7035,12 +7035,12 @@
       </c>
       <c r="N124" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O124" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="N125" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O125" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="N126" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O126" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="N127" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7255,12 +7255,12 @@
       </c>
       <c r="N128" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O128" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7310,12 +7310,12 @@
       </c>
       <c r="N129" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7365,12 @@
       </c>
       <c r="N130" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O130" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="N131" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O131" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7475,12 +7475,12 @@
       </c>
       <c r="N132" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O132" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="N133" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O133" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="N134" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O134" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7640,12 +7640,12 @@
       </c>
       <c r="N135" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="N136" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O136" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7750,12 +7750,12 @@
       </c>
       <c r="N137" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O137" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7805,12 +7805,12 @@
       </c>
       <c r="N138" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O138" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="N139" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7915,12 +7915,12 @@
       </c>
       <c r="N140" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O140" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -7970,12 +7970,12 @@
       </c>
       <c r="N141" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O141" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="N142" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O142" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8080,12 +8080,12 @@
       </c>
       <c r="N143" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="N144" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O144" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8190,12 +8190,12 @@
       </c>
       <c r="N145" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8245,12 +8245,12 @@
       </c>
       <c r="N146" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O146" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       </c>
       <c r="N147" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="N148" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O148" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8410,12 +8410,12 @@
       </c>
       <c r="N149" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8465,12 +8465,12 @@
       </c>
       <c r="N150" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O150" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="N151" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="N152" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O152" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="N153" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O153" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="N154" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O154" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8740,12 +8740,12 @@
       </c>
       <c r="N155" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O155" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8795,12 +8795,12 @@
       </c>
       <c r="N156" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O156" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="N157" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="N158" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O158" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8960,12 +8960,12 @@
       </c>
       <c r="N159" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9015,12 +9015,12 @@
       </c>
       <c r="N160" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O160" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9070,12 +9070,12 @@
       </c>
       <c r="N161" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9125,12 +9125,12 @@
       </c>
       <c r="N162" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O162" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="N163" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9235,12 +9235,12 @@
       </c>
       <c r="N164" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O164" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9290,12 +9290,12 @@
       </c>
       <c r="N165" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="N166" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O166" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="N167" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="N168" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O168" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9510,12 +9510,12 @@
       </c>
       <c r="N169" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O169" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9565,12 +9565,12 @@
       </c>
       <c r="N170" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O170" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9620,12 +9620,12 @@
       </c>
       <c r="N171" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="N172" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O172" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9730,12 +9730,12 @@
       </c>
       <c r="N173" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9785,12 +9785,12 @@
       </c>
       <c r="N174" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O174" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9840,12 +9840,12 @@
       </c>
       <c r="N175" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9895,12 +9895,12 @@
       </c>
       <c r="N176" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O176" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="N177" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="N178" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O178" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="N179" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O179" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10115,12 +10115,12 @@
       </c>
       <c r="N180" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O180" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="N181" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O181" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="N182" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O182" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="N183" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O183" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="N184" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O184" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10390,12 +10390,12 @@
       </c>
       <c r="N185" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O185" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10445,12 +10445,12 @@
       </c>
       <c r="N186" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O186" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10500,12 +10500,12 @@
       </c>
       <c r="N187" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O187" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10555,12 +10555,12 @@
       </c>
       <c r="N188" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O188" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10610,12 +10610,12 @@
       </c>
       <c r="N189" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O189" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10665,12 +10665,12 @@
       </c>
       <c r="N190" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O190" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10720,12 +10720,12 @@
       </c>
       <c r="N191" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O191" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10775,12 +10775,12 @@
       </c>
       <c r="N192" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O192" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10830,12 +10830,12 @@
       </c>
       <c r="N193" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O193" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10885,12 +10885,12 @@
       </c>
       <c r="N194" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O194" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="N195" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O195" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -10995,12 +10995,12 @@
       </c>
       <c r="N196" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O196" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11050,12 +11050,12 @@
       </c>
       <c r="N197" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O197" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="N198" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O198" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11160,12 +11160,12 @@
       </c>
       <c r="N199" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O199" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="N200" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O200" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11270,12 +11270,12 @@
       </c>
       <c r="N201" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O201" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11325,12 +11325,12 @@
       </c>
       <c r="N202" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O202" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11380,12 @@
       </c>
       <c r="N203" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O203" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11435,12 +11435,12 @@
       </c>
       <c r="N204" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O204" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11490,12 +11490,12 @@
       </c>
       <c r="N205" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O205" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11545,12 +11545,12 @@
       </c>
       <c r="N206" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O206" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11600,12 +11600,12 @@
       </c>
       <c r="N207" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O207" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11655,12 +11655,12 @@
       </c>
       <c r="N208" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O208" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11710,12 +11710,12 @@
       </c>
       <c r="N209" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O209" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11765,12 +11765,12 @@
       </c>
       <c r="N210" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O210" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11820,12 +11820,12 @@
       </c>
       <c r="N211" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O211" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11875,12 +11875,12 @@
       </c>
       <c r="N212" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O212" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11930,12 +11930,12 @@
       </c>
       <c r="N213" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O213" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -11985,12 +11985,12 @@
       </c>
       <c r="N214" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O214" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12040,12 +12040,12 @@
       </c>
       <c r="N215" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O215" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12095,12 +12095,12 @@
       </c>
       <c r="N216" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O216" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12150,12 +12150,12 @@
       </c>
       <c r="N217" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O217" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12205,12 +12205,12 @@
       </c>
       <c r="N218" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O218" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12260,12 +12260,12 @@
       </c>
       <c r="N219" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O219" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12315,12 +12315,12 @@
       </c>
       <c r="N220" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O220" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12370,12 +12370,12 @@
       </c>
       <c r="N221" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O221" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="N222" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O222" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12480,12 +12480,12 @@
       </c>
       <c r="N223" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O223" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12535,12 +12535,12 @@
       </c>
       <c r="N224" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O224" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12590,12 +12590,12 @@
       </c>
       <c r="N225" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O225" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12645,12 +12645,12 @@
       </c>
       <c r="N226" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O226" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12700,12 +12700,12 @@
       </c>
       <c r="N227" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O227" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12755,12 +12755,12 @@
       </c>
       <c r="N228" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O228" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="N229" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O229" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12865,12 +12865,12 @@
       </c>
       <c r="N230" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O230" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="N231" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O231" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -12975,12 +12975,12 @@
       </c>
       <c r="N232" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O232" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13030,12 +13030,12 @@
       </c>
       <c r="N233" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O233" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13085,12 +13085,12 @@
       </c>
       <c r="N234" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O234" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13140,12 +13140,12 @@
       </c>
       <c r="N235" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O235" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13195,12 +13195,12 @@
       </c>
       <c r="N236" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O236" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13250,12 +13250,12 @@
       </c>
       <c r="N237" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O237" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13305,12 +13305,12 @@
       </c>
       <c r="N238" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O238" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13360,12 +13360,12 @@
       </c>
       <c r="N239" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O239" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13415,12 +13415,12 @@
       </c>
       <c r="N240" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O240" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13470,12 +13470,12 @@
       </c>
       <c r="N241" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O241" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13525,12 +13525,12 @@
       </c>
       <c r="N242" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O242" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13580,12 +13580,12 @@
       </c>
       <c r="N243" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O243" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13635,12 +13635,12 @@
       </c>
       <c r="N244" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O244" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="N245" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O245" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="N246" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O246" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13800,12 +13800,12 @@
       </c>
       <c r="N247" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O247" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13855,12 +13855,12 @@
       </c>
       <c r="N248" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O248" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13910,12 +13910,12 @@
       </c>
       <c r="N249" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O249" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -13965,12 +13965,12 @@
       </c>
       <c r="N250" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O250" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14020,12 +14020,12 @@
       </c>
       <c r="N251" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O251" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14075,12 +14075,12 @@
       </c>
       <c r="N252" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O252" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14130,12 +14130,12 @@
       </c>
       <c r="N253" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O253" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14185,12 +14185,12 @@
       </c>
       <c r="N254" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O254" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14240,12 +14240,12 @@
       </c>
       <c r="N255" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O255" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="N256" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O256" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14350,12 +14350,12 @@
       </c>
       <c r="N257" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O257" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14405,12 +14405,12 @@
       </c>
       <c r="N258" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O258" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14460,12 +14460,12 @@
       </c>
       <c r="N259" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O259" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="N260" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O260" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14570,12 +14570,12 @@
       </c>
       <c r="N261" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O261" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14625,12 +14625,12 @@
       </c>
       <c r="N262" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O262" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14680,12 +14680,12 @@
       </c>
       <c r="N263" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O263" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14735,12 +14735,12 @@
       </c>
       <c r="N264" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O264" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14790,12 +14790,12 @@
       </c>
       <c r="N265" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O265" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14845,12 +14845,12 @@
       </c>
       <c r="N266" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O266" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14900,12 +14900,12 @@
       </c>
       <c r="N267" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O267" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -14955,12 +14955,12 @@
       </c>
       <c r="N268" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O268" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15010,12 +15010,12 @@
       </c>
       <c r="N269" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O269" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15065,12 +15065,12 @@
       </c>
       <c r="N270" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O270" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15120,12 +15120,12 @@
       </c>
       <c r="N271" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O271" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15175,12 +15175,12 @@
       </c>
       <c r="N272" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O272" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15230,12 +15230,12 @@
       </c>
       <c r="N273" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O273" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15285,12 +15285,12 @@
       </c>
       <c r="N274" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O274" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15340,12 +15340,12 @@
       </c>
       <c r="N275" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O275" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15395,12 +15395,12 @@
       </c>
       <c r="N276" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O276" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15450,12 +15450,12 @@
       </c>
       <c r="N277" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O277" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15505,12 +15505,12 @@
       </c>
       <c r="N278" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O278" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15560,12 +15560,12 @@
       </c>
       <c r="N279" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O279" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="N280" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O280" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15670,12 +15670,12 @@
       </c>
       <c r="N281" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O281" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15725,12 +15725,12 @@
       </c>
       <c r="N282" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O282" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15780,12 +15780,12 @@
       </c>
       <c r="N283" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O283" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15835,12 +15835,12 @@
       </c>
       <c r="N284" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O284" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15890,12 +15890,12 @@
       </c>
       <c r="N285" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O285" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -15945,12 +15945,12 @@
       </c>
       <c r="N286" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O286" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16000,12 +16000,12 @@
       </c>
       <c r="N287" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O287" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16055,12 +16055,12 @@
       </c>
       <c r="N288" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O288" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16110,12 +16110,12 @@
       </c>
       <c r="N289" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O289" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16165,12 +16165,12 @@
       </c>
       <c r="N290" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O290" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16220,12 +16220,12 @@
       </c>
       <c r="N291" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O291" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="N292" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O292" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16330,12 +16330,12 @@
       </c>
       <c r="N293" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O293" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16385,12 +16385,12 @@
       </c>
       <c r="N294" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O294" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16440,12 +16440,12 @@
       </c>
       <c r="N295" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O295" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16495,12 +16495,12 @@
       </c>
       <c r="N296" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O296" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16550,12 +16550,12 @@
       </c>
       <c r="N297" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O297" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16605,12 +16605,12 @@
       </c>
       <c r="N298" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O298" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16660,12 +16660,12 @@
       </c>
       <c r="N299" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O299" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="N300" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O300" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16770,12 +16770,12 @@
       </c>
       <c r="N301" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O301" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16825,12 +16825,12 @@
       </c>
       <c r="N302" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O302" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16880,12 +16880,12 @@
       </c>
       <c r="N303" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O303" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16935,12 +16935,12 @@
       </c>
       <c r="N304" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O304" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -16990,12 +16990,12 @@
       </c>
       <c r="N305" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O305" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17045,12 +17045,12 @@
       </c>
       <c r="N306" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O306" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17100,12 +17100,12 @@
       </c>
       <c r="N307" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O307" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17155,12 +17155,12 @@
       </c>
       <c r="N308" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O308" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17210,12 +17210,12 @@
       </c>
       <c r="N309" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O309" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17265,12 +17265,12 @@
       </c>
       <c r="N310" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O310" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17320,12 +17320,12 @@
       </c>
       <c r="N311" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O311" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17375,12 +17375,12 @@
       </c>
       <c r="N312" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O312" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17430,12 +17430,12 @@
       </c>
       <c r="N313" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O313" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17485,12 +17485,12 @@
       </c>
       <c r="N314" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O314" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="N315" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O315" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17595,12 +17595,12 @@
       </c>
       <c r="N316" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O316" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="N317" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O317" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="N318" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O318" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17760,12 +17760,12 @@
       </c>
       <c r="N319" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O319" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17815,12 +17815,12 @@
       </c>
       <c r="N320" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O320" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17870,12 +17870,12 @@
       </c>
       <c r="N321" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O321" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17925,12 +17925,12 @@
       </c>
       <c r="N322" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O322" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -17980,12 +17980,12 @@
       </c>
       <c r="N323" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O323" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18035,12 +18035,12 @@
       </c>
       <c r="N324" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O324" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18090,12 +18090,12 @@
       </c>
       <c r="N325" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O325" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18145,12 +18145,12 @@
       </c>
       <c r="N326" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O326" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18200,12 +18200,12 @@
       </c>
       <c r="N327" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O327" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18255,12 +18255,12 @@
       </c>
       <c r="N328" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O328" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18310,12 +18310,12 @@
       </c>
       <c r="N329" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O329" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18365,12 +18365,12 @@
       </c>
       <c r="N330" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O330" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18420,12 +18420,12 @@
       </c>
       <c r="N331" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O331" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18475,12 +18475,12 @@
       </c>
       <c r="N332" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O332" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18530,12 +18530,12 @@
       </c>
       <c r="N333" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O333" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18585,12 +18585,12 @@
       </c>
       <c r="N334" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O334" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18640,12 +18640,12 @@
       </c>
       <c r="N335" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O335" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18695,12 +18695,12 @@
       </c>
       <c r="N336" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O336" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18750,12 +18750,12 @@
       </c>
       <c r="N337" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O337" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18805,12 +18805,12 @@
       </c>
       <c r="N338" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O338" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18860,12 +18860,12 @@
       </c>
       <c r="N339" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O339" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18915,12 +18915,12 @@
       </c>
       <c r="N340" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O340" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -18970,12 +18970,12 @@
       </c>
       <c r="N341" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O341" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19025,12 +19025,12 @@
       </c>
       <c r="N342" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O342" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19080,12 +19080,12 @@
       </c>
       <c r="N343" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O343" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19135,12 +19135,12 @@
       </c>
       <c r="N344" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O344" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19190,12 +19190,12 @@
       </c>
       <c r="N345" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O345" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19245,12 +19245,12 @@
       </c>
       <c r="N346" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O346" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19300,12 +19300,12 @@
       </c>
       <c r="N347" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O347" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19355,12 +19355,12 @@
       </c>
       <c r="N348" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O348" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19410,12 +19410,12 @@
       </c>
       <c r="N349" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O349" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19465,12 +19465,12 @@
       </c>
       <c r="N350" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O350" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19520,12 +19520,12 @@
       </c>
       <c r="N351" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O351" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19575,12 +19575,12 @@
       </c>
       <c r="N352" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O352" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19630,12 +19630,12 @@
       </c>
       <c r="N353" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O353" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19685,12 +19685,12 @@
       </c>
       <c r="N354" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O354" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19740,12 +19740,12 @@
       </c>
       <c r="N355" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O355" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19795,12 +19795,12 @@
       </c>
       <c r="N356" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O356" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19850,12 +19850,12 @@
       </c>
       <c r="N357" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O357" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19905,12 +19905,12 @@
       </c>
       <c r="N358" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O358" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -19960,12 +19960,12 @@
       </c>
       <c r="N359" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O359" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20015,12 +20015,12 @@
       </c>
       <c r="N360" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O360" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20070,12 +20070,12 @@
       </c>
       <c r="N361" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O361" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20125,12 +20125,12 @@
       </c>
       <c r="N362" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O362" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20180,12 +20180,12 @@
       </c>
       <c r="N363" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O363" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20235,12 +20235,12 @@
       </c>
       <c r="N364" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O364" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20290,12 +20290,12 @@
       </c>
       <c r="N365" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O365" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20345,12 +20345,12 @@
       </c>
       <c r="N366" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O366" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20400,12 +20400,12 @@
       </c>
       <c r="N367" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O367" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20455,12 +20455,12 @@
       </c>
       <c r="N368" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O368" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20510,12 +20510,12 @@
       </c>
       <c r="N369" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O369" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20565,12 +20565,12 @@
       </c>
       <c r="N370" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O370" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20620,12 +20620,12 @@
       </c>
       <c r="N371" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O371" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20675,12 +20675,12 @@
       </c>
       <c r="N372" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O372" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20730,12 +20730,12 @@
       </c>
       <c r="N373" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O373" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20785,12 +20785,12 @@
       </c>
       <c r="N374" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O374" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20840,12 +20840,12 @@
       </c>
       <c r="N375" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O375" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20895,12 +20895,12 @@
       </c>
       <c r="N376" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O376" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -20950,12 +20950,12 @@
       </c>
       <c r="N377" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O377" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21005,12 +21005,12 @@
       </c>
       <c r="N378" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O378" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21060,12 +21060,12 @@
       </c>
       <c r="N379" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O379" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21115,12 +21115,12 @@
       </c>
       <c r="N380" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O380" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21170,12 +21170,12 @@
       </c>
       <c r="N381" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O381" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21225,12 +21225,12 @@
       </c>
       <c r="N382" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O382" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21280,12 +21280,12 @@
       </c>
       <c r="N383" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O383" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="N384" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O384" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21390,12 +21390,12 @@
       </c>
       <c r="N385" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O385" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21445,12 +21445,12 @@
       </c>
       <c r="N386" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O386" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21500,12 +21500,12 @@
       </c>
       <c r="N387" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O387" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21557,12 +21557,12 @@
       </c>
       <c r="N388" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O388" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21614,12 +21614,12 @@
       </c>
       <c r="N389" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O389" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="N390" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O390" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21728,12 +21728,12 @@
       </c>
       <c r="N391" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O391" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21785,12 +21785,12 @@
       </c>
       <c r="N392" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O392" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="N393" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O393" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21899,12 +21899,12 @@
       </c>
       <c r="N394" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O394" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="N395" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O395" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22013,12 +22013,12 @@
       </c>
       <c r="N396" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O396" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22070,12 +22070,12 @@
       </c>
       <c r="N397" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O397" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22127,12 +22127,12 @@
       </c>
       <c r="N398" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O398" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22184,12 +22184,12 @@
       </c>
       <c r="N399" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O399" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="N400" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O400" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22298,12 +22298,12 @@
       </c>
       <c r="N401" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O401" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22317,31 +22317,31 @@
         <v>46023</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>100.928378</v>
+        <v>100.966772</v>
       </c>
       <c r="D402" s="7" t="n">
         <v>-0.008999999999999999</v>
       </c>
       <c r="E402" s="7" t="n">
-        <v>-0.004145</v>
+        <v>-0.003766</v>
       </c>
       <c r="F402" s="6" t="n">
-        <v>108.126039</v>
+        <v>106.962618</v>
       </c>
       <c r="G402" s="7" t="n">
-        <v>-0.007499</v>
+        <v>-0.018179</v>
       </c>
       <c r="H402" s="6" t="n">
-        <v>96.616709</v>
+        <v>96.713674</v>
       </c>
       <c r="I402" s="7" t="n">
-        <v>-0.011118</v>
+        <v>-0.010125</v>
       </c>
       <c r="J402" s="6" t="n">
-        <v>102.976582</v>
+        <v>103.048661</v>
       </c>
       <c r="K402" s="7" t="n">
-        <v>-0.00019</v>
+        <v>0.00051</v>
       </c>
       <c r="L402" s="8" t="inlineStr">
         <is>
@@ -22355,12 +22355,12 @@
       </c>
       <c r="N402" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O402" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22374,31 +22374,31 @@
         <v>46054</v>
       </c>
       <c r="C403" s="9" t="n">
-        <v>100.121986</v>
+        <v>100.142756</v>
       </c>
       <c r="D403" s="10" t="n">
         <v>0.001</v>
       </c>
       <c r="E403" s="10" t="n">
-        <v>-0.003679</v>
+        <v>-0.003473</v>
       </c>
       <c r="F403" s="9" t="n">
-        <v>95.56461400000001</v>
+        <v>94.80753300000001</v>
       </c>
       <c r="G403" s="10" t="n">
-        <v>-0.001673</v>
+        <v>-0.009582</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>95.80434200000001</v>
+        <v>95.976523</v>
       </c>
       <c r="I403" s="10" t="n">
-        <v>-0.012383</v>
+        <v>-0.010608</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>102.82848</v>
+        <v>102.806579</v>
       </c>
       <c r="K403" s="10" t="n">
-        <v>0.000885</v>
+        <v>0.000672</v>
       </c>
       <c r="L403" s="11" t="inlineStr">
         <is>
@@ -22412,12 +22412,12 @@
       </c>
       <c r="N403" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O403" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22431,31 +22431,31 @@
         <v>46082</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>106.956932</v>
+        <v>106.738735</v>
       </c>
       <c r="D404" s="7" t="n">
         <v>0.004</v>
       </c>
       <c r="E404" s="7" t="n">
-        <v>0.014122</v>
+        <v>0.012053</v>
       </c>
       <c r="F404" s="6" t="n">
-        <v>97.417171</v>
+        <v>96.176647</v>
       </c>
       <c r="G404" s="7" t="n">
-        <v>0.01772</v>
+        <v>0.00476</v>
       </c>
       <c r="H404" s="6" t="n">
-        <v>102.749283</v>
+        <v>102.854397</v>
       </c>
       <c r="I404" s="7" t="n">
-        <v>-0.012617</v>
+        <v>-0.011606</v>
       </c>
       <c r="J404" s="6" t="n">
-        <v>109.878524</v>
+        <v>109.53363</v>
       </c>
       <c r="K404" s="7" t="n">
-        <v>0.02874</v>
+        <v>0.025511</v>
       </c>
       <c r="L404" s="8" t="inlineStr">
         <is>
@@ -22469,12 +22469,12 @@
       </c>
       <c r="N404" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O404" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22488,31 +22488,31 @@
         <v>46113</v>
       </c>
       <c r="C405" s="9" t="n">
-        <v>106.675953</v>
+        <v>106.613699</v>
       </c>
       <c r="D405" s="10" t="n">
         <v>0.012</v>
       </c>
       <c r="E405" s="10" t="n">
-        <v>0.025641</v>
+        <v>0.025042</v>
       </c>
       <c r="F405" s="9" t="n">
-        <v>105.79092</v>
+        <v>104.643588</v>
       </c>
       <c r="G405" s="10" t="n">
-        <v>0.110049</v>
+        <v>0.09801</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>102.560372</v>
+        <v>102.558775</v>
       </c>
       <c r="I405" s="10" t="n">
-        <v>0.023517</v>
+        <v>0.023501</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>109.063075</v>
+        <v>109.026816</v>
       </c>
       <c r="K405" s="10" t="n">
-        <v>0.022572</v>
+        <v>0.022232</v>
       </c>
       <c r="L405" s="11" t="inlineStr">
         <is>
@@ -22526,12 +22526,12 @@
       </c>
       <c r="N405" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O405" s="11" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -22545,31 +22545,31 @@
         <v>46143</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>108.595752</v>
+        <v>108.549177</v>
       </c>
       <c r="D406" s="7" t="n">
         <v>-0.003</v>
       </c>
       <c r="E406" s="7" t="n">
-        <v>0.011059</v>
+        <v>0.010626</v>
       </c>
       <c r="F406" s="6" t="n">
-        <v>128.172225</v>
+        <v>125.659794</v>
       </c>
       <c r="G406" s="7" t="n">
-        <v>0.075501</v>
+        <v>0.054419</v>
       </c>
       <c r="H406" s="6" t="n">
-        <v>103.718881</v>
+        <v>103.810617</v>
       </c>
       <c r="I406" s="7" t="n">
-        <v>-0.006678</v>
+        <v>-0.0058</v>
       </c>
       <c r="J406" s="6" t="n">
-        <v>110.275365</v>
+        <v>110.287602</v>
       </c>
       <c r="K406" s="7" t="n">
-        <v>0.016815</v>
+        <v>0.016928</v>
       </c>
       <c r="L406" s="8" t="inlineStr">
         <is>
@@ -22583,12 +22583,69 @@
       </c>
       <c r="N406" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
         </is>
       </c>
       <c r="O406" s="8" t="inlineStr">
         <is>
-          <t>23 de julio de 2026</t>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="4" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B407" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C407" s="9" t="n">
+        <v>107.449582</v>
+      </c>
+      <c r="D407" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="E407" s="10" t="n">
+        <v>0.028191</v>
+      </c>
+      <c r="F407" s="9" t="n">
+        <v>111.293453</v>
+      </c>
+      <c r="G407" s="10" t="n">
+        <v>0.00496</v>
+      </c>
+      <c r="H407" s="9" t="n">
+        <v>102.597063</v>
+      </c>
+      <c r="I407" s="10" t="n">
+        <v>0.017117</v>
+      </c>
+      <c r="J407" s="9" t="n">
+        <v>109.991856</v>
+      </c>
+      <c r="K407" s="10" t="n">
+        <v>0.035514</v>
+      </c>
+      <c r="L407" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="M407" s="11" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="N407" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/igae/igae2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="O407" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
